--- a/perawat.xlsx
+++ b/perawat.xlsx
@@ -459,14 +459,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C2" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -477,14 +477,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -495,14 +495,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -513,14 +513,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C5" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -531,14 +531,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -549,14 +549,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -567,14 +567,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C8" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C9" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -603,14 +603,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -621,14 +621,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -639,14 +639,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -657,14 +657,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -675,14 +675,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -693,14 +693,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -711,14 +711,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -729,14 +729,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -747,14 +747,14 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -765,14 +765,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -783,10 +783,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="C20" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -801,14 +801,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C21" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -819,14 +819,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C22" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -855,14 +855,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -873,14 +873,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C25" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -891,14 +891,14 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C26" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -909,14 +909,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -927,14 +927,14 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>50</v>
+        <v>28</v>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -945,14 +945,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>23</v>
+        <v>53</v>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -963,14 +963,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -981,10 +981,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="C31" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -999,14 +999,14 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="C32" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1017,14 +1017,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -1035,14 +1035,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1053,14 +1053,14 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C35" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1071,14 +1071,14 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C36" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1089,14 +1089,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C37" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1107,14 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C38" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1125,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="C39" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1143,14 +1143,14 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C40" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -1161,14 +1161,14 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C41" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1179,14 +1179,14 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="C42" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1197,14 +1197,14 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="C43" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1215,14 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="C44" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1233,14 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C45" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1251,14 +1251,14 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C46" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -1269,14 +1269,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c r="C47" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1287,14 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C48" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1305,14 +1305,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C49" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1323,14 +1323,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C50" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1341,14 +1341,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C51" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1359,14 +1359,14 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C52" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -1377,14 +1377,14 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1395,14 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="C54" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1413,14 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="C55" t="n">
         <v>7</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -1431,14 +1431,14 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>26</v>
+        <v>46</v>
       </c>
       <c r="C56" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1449,14 +1449,14 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C57" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1467,14 +1467,14 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C58" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1485,14 +1485,14 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>43</v>
+        <v>59</v>
       </c>
       <c r="C59" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1503,14 +1503,14 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C60" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1521,14 +1521,14 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1539,14 +1539,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C62" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C63" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C65" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C66" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1632,11 +1632,11 @@
         <v>25</v>
       </c>
       <c r="C67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1647,14 +1647,14 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C68" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1665,14 +1665,14 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="C69" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C70" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -1701,14 +1701,14 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C71" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="C72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1737,14 +1737,14 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="C73" t="n">
         <v>2</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C74" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -1773,14 +1773,14 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C75" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1791,14 +1791,14 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1809,14 +1809,14 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C77" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1827,14 +1827,14 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C78" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1845,14 +1845,14 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C79" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1863,14 +1863,14 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C80" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1881,14 +1881,14 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="C81" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -1899,14 +1899,14 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C82" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1917,14 +1917,14 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C83" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1935,14 +1935,14 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C84" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1953,14 +1953,14 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>54</v>
+        <v>41</v>
       </c>
       <c r="C85" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1971,14 +1971,14 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C86" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1989,14 +1989,14 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2007,10 +2007,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C88" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -2025,14 +2025,14 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="C89" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2043,10 +2043,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="C90" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -2061,14 +2061,14 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="C91" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2097,14 +2097,14 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C93" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2115,14 +2115,14 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C94" t="n">
         <v>4</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2133,14 +2133,14 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C95" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2151,14 +2151,14 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="C96" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -2169,14 +2169,14 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C97" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -2187,14 +2187,14 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="C98" t="n">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -2205,14 +2205,14 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C100" t="n">
         <v>10</v>
@@ -2241,14 +2241,14 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C101" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -2259,14 +2259,14 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C102" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2277,14 +2277,14 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="C103" t="n">
         <v>4</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -2295,14 +2295,14 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C104" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2313,14 +2313,14 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C105" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2331,14 +2331,14 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="C106" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C107" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -2367,14 +2367,14 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C108" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2385,14 +2385,14 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="C109" t="n">
         <v>1</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -2403,14 +2403,14 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C110" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2421,14 +2421,14 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C111" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2439,14 +2439,14 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>24</v>
+        <v>53</v>
       </c>
       <c r="C112" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -2457,14 +2457,14 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C113" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2475,14 +2475,14 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>33</v>
+        <v>60</v>
       </c>
       <c r="C114" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2493,14 +2493,14 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="C115" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2511,10 +2511,10 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="C116" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -2529,14 +2529,14 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C117" t="n">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2547,14 +2547,14 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C118" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2565,14 +2565,14 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C119" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2583,10 +2583,10 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C120" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C121" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2619,14 +2619,14 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C122" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -2637,10 +2637,10 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -2655,14 +2655,14 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C124" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2673,14 +2673,14 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C125" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2691,10 +2691,10 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C126" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -2709,14 +2709,14 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C127" t="n">
-        <v>24</v>
+        <v>3</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2727,14 +2727,14 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>53</v>
+        <v>34</v>
       </c>
       <c r="C128" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -2745,14 +2745,14 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C129" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2763,14 +2763,14 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C130" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -2781,14 +2781,14 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C131" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2799,14 +2799,14 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2817,14 +2817,14 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C133" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -2835,14 +2835,14 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C134" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -2853,14 +2853,14 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C135" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -2871,14 +2871,14 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C136" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2889,14 +2889,14 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C137" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -2907,14 +2907,14 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C138" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -2925,14 +2925,14 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C139" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2943,14 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C140" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2961,14 +2961,14 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="C141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2979,14 +2979,14 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C142" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -2997,14 +2997,14 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C143" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3015,14 +3015,14 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C144" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -3033,14 +3033,14 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C145" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3051,14 +3051,14 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="C146" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -3069,14 +3069,14 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C147" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -3087,14 +3087,14 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C148" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -3105,14 +3105,14 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="C149" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -3123,14 +3123,14 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C150" t="n">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -3141,14 +3141,14 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="C151" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="C152" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3177,14 +3177,14 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="C153" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -3195,14 +3195,14 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C154" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3213,14 +3213,14 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="C155" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3231,14 +3231,14 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="C156" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3249,14 +3249,14 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C157" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -3267,14 +3267,14 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C158" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3285,14 +3285,14 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C159" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3303,14 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C160" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3321,14 +3321,14 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C161" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C162" t="n">
         <v>5</v>
@@ -3357,14 +3357,14 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C163" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -3375,14 +3375,14 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>58</v>
+        <v>26</v>
       </c>
       <c r="C164" t="n">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -3393,14 +3393,14 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C165" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3411,14 +3411,14 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>28</v>
+        <v>49</v>
       </c>
       <c r="C166" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3429,14 +3429,14 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>60</v>
+        <v>38</v>
       </c>
       <c r="C167" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3447,14 +3447,14 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C168" t="n">
         <v>1</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3465,14 +3465,14 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C169" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3483,14 +3483,14 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C170" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3501,14 +3501,14 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C171" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -3519,14 +3519,14 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C172" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -3537,14 +3537,14 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="C173" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
       <c r="C174" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -3573,14 +3573,14 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C175" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -3591,14 +3591,14 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C176" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3609,14 +3609,14 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C177" t="n">
         <v>3</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3627,14 +3627,14 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="C178" t="n">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3645,14 +3645,14 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="C179" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3663,14 +3663,14 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C180" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3684,11 +3684,11 @@
         <v>35</v>
       </c>
       <c r="C181" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="C182" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -3717,14 +3717,14 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C183" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3735,14 +3735,14 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="C184" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3753,14 +3753,14 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C185" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3771,14 +3771,14 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C186" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3789,14 +3789,14 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="C187" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -3807,14 +3807,14 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C188" t="n">
         <v>3</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3825,14 +3825,14 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C189" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3843,10 +3843,10 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="C190" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -3861,14 +3861,14 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C191" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -3879,14 +3879,14 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>56</v>
+        <v>32</v>
       </c>
       <c r="C192" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3897,14 +3897,14 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C193" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -3915,10 +3915,10 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -3933,14 +3933,14 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>59</v>
+        <v>39</v>
       </c>
       <c r="C195" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3954,11 +3954,11 @@
         <v>43</v>
       </c>
       <c r="C196" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3969,14 +3969,14 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C197" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3987,14 +3987,14 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C198" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -4005,14 +4005,14 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C199" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4023,14 +4023,14 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C200" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4041,14 +4041,14 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C201" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4059,14 +4059,14 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="C202" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4077,14 +4077,14 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C203" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -4095,14 +4095,14 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C204" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -4113,14 +4113,14 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C205" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -4131,14 +4131,14 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="C206" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4149,14 +4149,14 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C207" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -4167,14 +4167,14 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C208" t="n">
         <v>10</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -4185,14 +4185,14 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C209" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4203,14 +4203,14 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C210" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4221,14 +4221,14 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="C211" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -4239,14 +4239,14 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="C212" t="n">
         <v>3</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -4257,14 +4257,14 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>59</v>
+        <v>26</v>
       </c>
       <c r="C213" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -4275,14 +4275,14 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="C214" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4293,14 +4293,14 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C215" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -4311,14 +4311,14 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C216" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4329,14 +4329,14 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C217" t="n">
         <v>2</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -4347,14 +4347,14 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="C218" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -4365,14 +4365,14 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C219" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -4383,14 +4383,14 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C220" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -4401,14 +4401,14 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C221" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -4419,14 +4419,14 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C222" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -4440,11 +4440,11 @@
         <v>46</v>
       </c>
       <c r="C223" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4455,14 +4455,14 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="C224" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4473,14 +4473,14 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C225" t="n">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4491,14 +4491,14 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C226" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4509,14 +4509,14 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4527,14 +4527,14 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C228" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="C229" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -4563,14 +4563,14 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C230" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4581,14 +4581,14 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C231" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -4599,14 +4599,14 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="C232" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -4617,14 +4617,14 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C233" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -4635,14 +4635,14 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="C234" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4653,7 +4653,7 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="C235" t="n">
         <v>2</v>
@@ -4671,14 +4671,14 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C236" t="n">
         <v>1</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4689,14 +4689,14 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="C237" t="n">
         <v>6</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4707,14 +4707,14 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C238" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4725,14 +4725,14 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C239" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4743,14 +4743,14 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>29</v>
+        <v>57</v>
       </c>
       <c r="C240" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4761,14 +4761,14 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C241" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4779,14 +4779,14 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C242" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -4797,14 +4797,14 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C243" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4815,14 +4815,14 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C244" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4833,10 +4833,10 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="C245" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -4851,14 +4851,14 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C246" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4869,14 +4869,14 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="C247" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4887,14 +4887,14 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="C248" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -4905,14 +4905,14 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C249" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4923,14 +4923,14 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C250" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4941,14 +4941,14 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C251" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -4959,14 +4959,14 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C252" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4977,10 +4977,10 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C253" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -4998,11 +4998,11 @@
         <v>29</v>
       </c>
       <c r="C254" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -5013,14 +5013,14 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C255" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -5031,14 +5031,14 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C256" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -5049,10 +5049,10 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C257" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -5067,14 +5067,14 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C258" t="n">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -5085,14 +5085,14 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="C259" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -5103,14 +5103,14 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C260" t="n">
-        <v>29</v>
+        <v>4</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -5121,14 +5121,14 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C261" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -5139,14 +5139,14 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>57</v>
+        <v>23</v>
       </c>
       <c r="C262" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -5157,14 +5157,14 @@
         </is>
       </c>
       <c r="B263" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="C263" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -5175,14 +5175,14 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="C264" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -5193,14 +5193,14 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -5211,14 +5211,14 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C266" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -5229,10 +5229,10 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C267" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -5247,14 +5247,14 @@
         </is>
       </c>
       <c r="B268" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C268" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -5265,14 +5265,14 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="C269" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -5283,14 +5283,14 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>49</v>
+        <v>24</v>
       </c>
       <c r="C270" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -5301,14 +5301,14 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C271" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -5319,14 +5319,14 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C272" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -5337,14 +5337,14 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C273" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -5355,14 +5355,14 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C274" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -5373,14 +5373,14 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>41</v>
+        <v>58</v>
       </c>
       <c r="C275" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -5391,14 +5391,14 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C276" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5446,16 +5446,6 @@
       </c>
       <c r="B3" t="n">
         <v>12</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Perawat_275</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -5469,7 +5459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5504,16 +5494,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Perawat_275</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/perawat.xlsx
+++ b/perawat.xlsx
@@ -459,14 +459,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -477,14 +477,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="C3" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -495,14 +495,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="C4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -513,10 +513,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C5" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -531,14 +531,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -549,14 +549,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="C7" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -567,14 +567,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -585,14 +585,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -603,14 +603,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -621,14 +621,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -639,14 +639,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -657,10 +657,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C13" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -675,14 +675,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -693,14 +693,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -711,14 +711,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C16" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -729,14 +729,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -747,10 +747,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C18" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -765,14 +765,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -783,14 +783,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C20" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -801,14 +801,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -822,11 +822,11 @@
         <v>24</v>
       </c>
       <c r="C22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -837,14 +837,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="C23" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -855,14 +855,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -873,14 +873,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C25" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -891,14 +891,14 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="C27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -927,14 +927,14 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -945,14 +945,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C29" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -963,14 +963,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C30" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -981,14 +981,14 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C31" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -999,14 +999,14 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C32" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1017,14 +1017,14 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C33" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1035,14 +1035,14 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="C34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1053,14 +1053,14 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="C35" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C36" t="n">
         <v>17</v>
@@ -1089,14 +1089,14 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
       <c r="C37" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1107,14 +1107,14 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="C38" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -1125,14 +1125,14 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="C39" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1143,14 +1143,14 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C40" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C41" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1179,10 +1179,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C42" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1197,14 +1197,14 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27</v>
+        <v>59</v>
       </c>
       <c r="C43" t="n">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1215,14 +1215,14 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C44" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1233,14 +1233,14 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>54</v>
+        <v>31</v>
       </c>
       <c r="C45" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -1251,14 +1251,14 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -1269,14 +1269,14 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1287,14 +1287,14 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C48" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1305,14 +1305,14 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1323,14 +1323,14 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1341,14 +1341,14 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C51" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1359,14 +1359,14 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C52" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1377,14 +1377,14 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C53" t="n">
         <v>2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -1395,14 +1395,14 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C54" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -1413,14 +1413,14 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C55" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1431,14 +1431,14 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C56" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1449,14 +1449,14 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="C57" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1467,14 +1467,14 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C58" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1485,14 +1485,14 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1503,14 +1503,14 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C60" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1524,11 +1524,11 @@
         <v>60</v>
       </c>
       <c r="C61" t="n">
-        <v>33</v>
+        <v>6</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1539,14 +1539,14 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1557,14 +1557,14 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C63" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1575,10 +1575,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C64" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -1593,14 +1593,14 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C65" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1611,14 +1611,14 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C66" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -1629,14 +1629,14 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C67" t="n">
         <v>2</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -1647,14 +1647,14 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C68" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1665,14 +1665,14 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C69" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1683,14 +1683,14 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C70" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1701,14 +1701,14 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C71" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1719,10 +1719,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C72" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -1737,14 +1737,14 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C73" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -1755,14 +1755,14 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="C74" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1773,14 +1773,14 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C75" t="n">
         <v>3</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -1791,14 +1791,14 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C76" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1809,14 +1809,14 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C77" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1827,14 +1827,14 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="C78" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -1845,14 +1845,14 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C79" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -1863,14 +1863,14 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C80" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -1881,14 +1881,14 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C81" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1899,14 +1899,14 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C82" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1917,14 +1917,14 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c r="C83" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1935,14 +1935,14 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="C84" t="n">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -1953,14 +1953,14 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
       <c r="C85" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -1971,14 +1971,14 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C86" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -1989,14 +1989,14 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C87" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -2007,14 +2007,14 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="C88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2025,14 +2025,14 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="C89" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2043,14 +2043,14 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="C90" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -2061,14 +2061,14 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>33</v>
+        <v>58</v>
       </c>
       <c r="C91" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>30</v>
+        <v>54</v>
       </c>
       <c r="C92" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -2097,14 +2097,14 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2115,7 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C94" t="n">
         <v>4</v>
@@ -2133,14 +2133,14 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="C95" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2151,14 +2151,14 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C96" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2169,14 +2169,14 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>40</v>
+        <v>59</v>
       </c>
       <c r="C97" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2187,14 +2187,14 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C98" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -2205,14 +2205,14 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="C99" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -2223,14 +2223,14 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>58</v>
+        <v>22</v>
       </c>
       <c r="C100" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2241,14 +2241,14 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C101" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2259,14 +2259,14 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="C102" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -2277,14 +2277,14 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>60</v>
+        <v>22</v>
       </c>
       <c r="C103" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -2295,10 +2295,10 @@
         </is>
       </c>
       <c r="B104" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C104" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -2313,10 +2313,10 @@
         </is>
       </c>
       <c r="B105" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="C105" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -2331,14 +2331,14 @@
         </is>
       </c>
       <c r="B106" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="C106" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -2349,14 +2349,14 @@
         </is>
       </c>
       <c r="B107" t="n">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="C107" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -2367,14 +2367,14 @@
         </is>
       </c>
       <c r="B108" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C108" t="n">
         <v>8</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -2385,14 +2385,14 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="C109" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C110" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -2421,14 +2421,14 @@
         </is>
       </c>
       <c r="B111" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="C111" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2439,14 +2439,14 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>53</v>
+        <v>26</v>
       </c>
       <c r="C112" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2457,14 +2457,14 @@
         </is>
       </c>
       <c r="B113" t="n">
-        <v>51</v>
+        <v>24</v>
       </c>
       <c r="C113" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -2475,14 +2475,14 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="C114" t="n">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -2493,14 +2493,14 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="C115" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2511,14 +2511,14 @@
         </is>
       </c>
       <c r="B116" t="n">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C116" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2529,14 +2529,14 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>25</v>
+        <v>49</v>
       </c>
       <c r="C117" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2547,14 +2547,14 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="C118" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2565,14 +2565,14 @@
         </is>
       </c>
       <c r="B119" t="n">
-        <v>26</v>
+        <v>58</v>
       </c>
       <c r="C119" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2583,14 +2583,14 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C120" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2601,14 +2601,14 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="C121" t="n">
-        <v>12</v>
+        <v>33</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2619,14 +2619,14 @@
         </is>
       </c>
       <c r="B122" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C122" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -2637,14 +2637,14 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="C123" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="C124" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -2673,14 +2673,14 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C125" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2691,14 +2691,14 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C126" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C127" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -2727,14 +2727,14 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="C128" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2745,14 +2745,14 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>27</v>
+        <v>52</v>
       </c>
       <c r="C129" t="n">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -2763,14 +2763,14 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C130" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -2781,14 +2781,14 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C131" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -2799,14 +2799,14 @@
         </is>
       </c>
       <c r="B132" t="n">
-        <v>23</v>
+        <v>55</v>
       </c>
       <c r="C132" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -2817,14 +2817,14 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C133" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -2835,14 +2835,14 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C134" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2853,14 +2853,14 @@
         </is>
       </c>
       <c r="B135" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="C135" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2871,14 +2871,14 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="C136" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -2889,14 +2889,14 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C137" t="n">
         <v>9</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -2907,14 +2907,14 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C138" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -2925,14 +2925,14 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="C139" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2943,14 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="C140" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
         <v>23</v>
       </c>
       <c r="C141" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -2979,14 +2979,14 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C142" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -2997,14 +2997,14 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C143" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -3015,14 +3015,14 @@
         </is>
       </c>
       <c r="B144" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C144" t="n">
         <v>1</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -3033,14 +3033,14 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C145" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -3051,14 +3051,14 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="C146" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -3069,14 +3069,14 @@
         </is>
       </c>
       <c r="B147" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C147" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3087,14 +3087,14 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="C148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3105,14 +3105,14 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C149" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3123,14 +3123,14 @@
         </is>
       </c>
       <c r="B150" t="n">
-        <v>58</v>
+        <v>38</v>
       </c>
       <c r="C150" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3141,14 +3141,14 @@
         </is>
       </c>
       <c r="B151" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C151" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3159,14 +3159,14 @@
         </is>
       </c>
       <c r="B152" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C152" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3177,14 +3177,14 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="C153" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -3195,14 +3195,14 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C154" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -3213,14 +3213,14 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C155" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C156" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -3249,10 +3249,10 @@
         </is>
       </c>
       <c r="B157" t="n">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C157" t="n">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -3267,14 +3267,14 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C158" t="n">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -3285,14 +3285,14 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C159" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3303,14 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C160" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -3321,14 +3321,14 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="C161" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3339,10 +3339,10 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="C162" t="n">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -3357,14 +3357,14 @@
         </is>
       </c>
       <c r="B163" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C163" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3375,14 +3375,14 @@
         </is>
       </c>
       <c r="B164" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C164" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -3393,14 +3393,14 @@
         </is>
       </c>
       <c r="B165" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C165" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -3411,14 +3411,14 @@
         </is>
       </c>
       <c r="B166" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="C166" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -3429,14 +3429,14 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C167" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3447,14 +3447,14 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="C168" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3465,14 +3465,14 @@
         </is>
       </c>
       <c r="B169" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C169" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -3483,14 +3483,14 @@
         </is>
       </c>
       <c r="B170" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="C170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3501,14 +3501,14 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="C171" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3519,14 +3519,14 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C172" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3537,14 +3537,14 @@
         </is>
       </c>
       <c r="B173" t="n">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="C173" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -3555,10 +3555,10 @@
         </is>
       </c>
       <c r="B174" t="n">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C174" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -3573,14 +3573,14 @@
         </is>
       </c>
       <c r="B175" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="C175" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3591,14 +3591,14 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C176" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3609,14 +3609,14 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="C177" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3627,14 +3627,14 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="C178" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3645,14 +3645,14 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>59</v>
+        <v>29</v>
       </c>
       <c r="C179" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, gigi</t>
         </is>
       </c>
     </row>
@@ -3663,14 +3663,14 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>53</v>
+        <v>35</v>
       </c>
       <c r="C180" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -3681,14 +3681,14 @@
         </is>
       </c>
       <c r="B181" t="n">
+        <v>60</v>
+      </c>
+      <c r="C181" t="n">
         <v>35</v>
       </c>
-      <c r="C181" t="n">
-        <v>9</v>
-      </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3699,14 +3699,14 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="C182" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3717,14 +3717,14 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C183" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3735,14 +3735,14 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C184" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -3753,14 +3753,14 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>56</v>
+        <v>28</v>
       </c>
       <c r="C185" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3771,14 +3771,14 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="C186" t="n">
         <v>4</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3789,14 +3789,14 @@
         </is>
       </c>
       <c r="B187" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="C187" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -3807,14 +3807,14 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C188" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -3825,14 +3825,14 @@
         </is>
       </c>
       <c r="B189" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="C189" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -3843,14 +3843,14 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C190" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -3861,14 +3861,14 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C191" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -3879,14 +3879,14 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="C192" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3897,14 +3897,14 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C193" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -3915,14 +3915,14 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="C194" t="n">
         <v>2</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -3933,14 +3933,14 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C195" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3951,14 +3951,14 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="C196" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -3969,14 +3969,14 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="C197" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -3987,14 +3987,14 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C198" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4005,10 +4005,10 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>47</v>
+        <v>58</v>
       </c>
       <c r="C199" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -4023,14 +4023,14 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="C200" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -4041,14 +4041,14 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C201" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4059,14 +4059,14 @@
         </is>
       </c>
       <c r="B202" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C202" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -4077,14 +4077,14 @@
         </is>
       </c>
       <c r="B203" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C203" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4095,14 +4095,14 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C204" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>gigi, icu</t>
         </is>
       </c>
     </row>
@@ -4113,14 +4113,14 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C205" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -4131,14 +4131,14 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>60</v>
+        <v>33</v>
       </c>
       <c r="C206" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -4149,14 +4149,14 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C207" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4167,14 +4167,14 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="C208" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -4185,14 +4185,14 @@
         </is>
       </c>
       <c r="B209" t="n">
+        <v>49</v>
+      </c>
+      <c r="C209" t="n">
         <v>25</v>
       </c>
-      <c r="C209" t="n">
-        <v>3</v>
-      </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4203,10 +4203,10 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>54</v>
+        <v>26</v>
       </c>
       <c r="C210" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -4221,14 +4221,14 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="C211" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4239,14 +4239,14 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C212" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4257,14 +4257,14 @@
         </is>
       </c>
       <c r="B213" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C213" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4275,14 +4275,14 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="C214" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -4293,14 +4293,14 @@
         </is>
       </c>
       <c r="B215" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C215" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4311,14 +4311,14 @@
         </is>
       </c>
       <c r="B216" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C216" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4329,14 +4329,14 @@
         </is>
       </c>
       <c r="B217" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C217" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4347,14 +4347,14 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C218" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4365,14 +4365,14 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C219" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -4383,14 +4383,14 @@
         </is>
       </c>
       <c r="B220" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C220" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -4401,14 +4401,14 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="C221" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>umum, bayi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4419,14 +4419,14 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="C222" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4437,14 +4437,14 @@
         </is>
       </c>
       <c r="B223" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C223" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4455,14 +4455,14 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="C224" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4473,10 +4473,10 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="C225" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -4491,14 +4491,14 @@
         </is>
       </c>
       <c r="B226" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="C226" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -4509,14 +4509,14 @@
         </is>
       </c>
       <c r="B227" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="C227" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4527,14 +4527,14 @@
         </is>
       </c>
       <c r="B228" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="C228" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>icu, bayi</t>
         </is>
       </c>
     </row>
@@ -4545,10 +4545,10 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="C229" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -4563,14 +4563,14 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C230" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4581,14 +4581,14 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C231" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>icu, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4599,14 +4599,14 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="C232" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>umum, gigi</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4617,14 +4617,14 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C233" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>22</v>
+        <v>57</v>
       </c>
       <c r="C234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -4653,14 +4653,14 @@
         </is>
       </c>
       <c r="B235" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C235" t="n">
         <v>2</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -4671,14 +4671,14 @@
         </is>
       </c>
       <c r="B236" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="C236" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu, gigi</t>
         </is>
       </c>
     </row>
@@ -4689,14 +4689,14 @@
         </is>
       </c>
       <c r="B237" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C237" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -4707,14 +4707,14 @@
         </is>
       </c>
       <c r="B238" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="C238" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -4725,14 +4725,14 @@
         </is>
       </c>
       <c r="B239" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C239" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4743,14 +4743,14 @@
         </is>
       </c>
       <c r="B240" t="n">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="C240" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -4761,14 +4761,14 @@
         </is>
       </c>
       <c r="B241" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C241" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4779,14 +4779,14 @@
         </is>
       </c>
       <c r="B242" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C242" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4797,14 +4797,14 @@
         </is>
       </c>
       <c r="B243" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="C243" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -4815,14 +4815,14 @@
         </is>
       </c>
       <c r="B244" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="C244" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -4833,14 +4833,14 @@
         </is>
       </c>
       <c r="B245" t="n">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="C245" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -4851,14 +4851,14 @@
         </is>
       </c>
       <c r="B246" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C246" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>gigi, umum</t>
         </is>
       </c>
     </row>
@@ -4869,14 +4869,14 @@
         </is>
       </c>
       <c r="B247" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C247" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -4887,14 +4887,14 @@
         </is>
       </c>
       <c r="B248" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C248" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -4905,14 +4905,14 @@
         </is>
       </c>
       <c r="B249" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C249" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi, umum</t>
         </is>
       </c>
     </row>
@@ -4923,14 +4923,14 @@
         </is>
       </c>
       <c r="B250" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="C250" t="n">
         <v>14</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4941,14 +4941,14 @@
         </is>
       </c>
       <c r="B251" t="n">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="C251" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -4959,10 +4959,10 @@
         </is>
       </c>
       <c r="B252" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C252" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -4977,14 +4977,14 @@
         </is>
       </c>
       <c r="B253" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C253" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -4995,14 +4995,14 @@
         </is>
       </c>
       <c r="B254" t="n">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C254" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>gigi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -5013,14 +5013,14 @@
         </is>
       </c>
       <c r="B255" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="C255" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -5031,14 +5031,14 @@
         </is>
       </c>
       <c r="B256" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C256" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>gigi, bayi</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -5049,14 +5049,14 @@
         </is>
       </c>
       <c r="B257" t="n">
-        <v>54</v>
+        <v>25</v>
       </c>
       <c r="C257" t="n">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -5067,14 +5067,14 @@
         </is>
       </c>
       <c r="B258" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="C258" t="n">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -5085,14 +5085,14 @@
         </is>
       </c>
       <c r="B259" t="n">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C259" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -5103,14 +5103,14 @@
         </is>
       </c>
       <c r="B260" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C260" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>bayi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -5121,14 +5121,14 @@
         </is>
       </c>
       <c r="B261" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C261" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>gigi, icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -5139,14 +5139,14 @@
         </is>
       </c>
       <c r="B262" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C262" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>umum, bayi</t>
         </is>
       </c>
     </row>
@@ -5160,11 +5160,11 @@
         <v>55</v>
       </c>
       <c r="C263" t="n">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>bayi, icu</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
         </is>
       </c>
       <c r="B264" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C264" t="n">
         <v>6</v>
@@ -5193,14 +5193,14 @@
         </is>
       </c>
       <c r="B265" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C265" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>icu, gigi</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -5211,14 +5211,14 @@
         </is>
       </c>
       <c r="B266" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C266" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>bayi</t>
         </is>
       </c>
     </row>
@@ -5229,14 +5229,14 @@
         </is>
       </c>
       <c r="B267" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="C267" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>icu</t>
+          <t>umum, icu</t>
         </is>
       </c>
     </row>
@@ -5250,11 +5250,11 @@
         <v>24</v>
       </c>
       <c r="C268" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>bayi, umum</t>
+          <t>umum</t>
         </is>
       </c>
     </row>
@@ -5265,14 +5265,14 @@
         </is>
       </c>
       <c r="B269" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C269" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>gigi, bayi</t>
         </is>
       </c>
     </row>
@@ -5283,14 +5283,14 @@
         </is>
       </c>
       <c r="B270" t="n">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C270" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>umum, icu</t>
+          <t>icu, umum</t>
         </is>
       </c>
     </row>
@@ -5301,14 +5301,14 @@
         </is>
       </c>
       <c r="B271" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C271" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>icu, umum</t>
+          <t>umum, gigi</t>
         </is>
       </c>
     </row>
@@ -5319,14 +5319,14 @@
         </is>
       </c>
       <c r="B272" t="n">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C272" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -5337,14 +5337,14 @@
         </is>
       </c>
       <c r="B273" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="C273" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>bayi, icu</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -5355,14 +5355,14 @@
         </is>
       </c>
       <c r="B274" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C274" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>gigi, umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -5373,14 +5373,14 @@
         </is>
       </c>
       <c r="B275" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C275" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>bayi, gigi</t>
+          <t>gigi</t>
         </is>
       </c>
     </row>
@@ -5391,14 +5391,14 @@
         </is>
       </c>
       <c r="B276" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="C276" t="n">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>umum</t>
+          <t>icu</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5446,6 +5446,16 @@
       </c>
       <c r="B3" t="n">
         <v>12</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Perawat 222</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -5459,7 +5469,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5494,6 +5504,16 @@
         <v>15</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Perawat 222</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
